--- a/backend/prueba.xlsx
+++ b/backend/prueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lizarazo\Downloads\sicetac idea web\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBCCEB8B-23CA-4329-AD4D-1E0A5E3ADEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FB3CBF-6100-4F32-B152-DCC7CB117088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4EEA28B7-B307-4C6B-A382-3F5C4D062489}"/>
   </bookViews>
@@ -454,84 +454,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FE573F3-977B-4B36-89ED-85D89E3644F6}">
-  <dimension ref="B1:I3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
         <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
       <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
         <v>12</v>
       </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
       <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
         <v>1</v>
       </c>
     </row>

--- a/backend/prueba.xlsx
+++ b/backend/prueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lizarazo\Downloads\sicetac idea web\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FB3CBF-6100-4F32-B152-DCC7CB117088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC62DD9-20AD-4DC0-8A3A-A0CACF25F238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4EEA28B7-B307-4C6B-A382-3F5C4D062489}"/>
   </bookViews>
@@ -96,7 +96,7 @@
     <t>ACHUMALAKA</t>
   </si>
   <si>
-    <t>ASA</t>
+    <t>cargado</t>
   </si>
 </sst>
 </file>
